--- a/2026-ECMFA/RQ1/results/experiment_run_gpt-4_1-mini.xlsx
+++ b/2026-ECMFA/RQ1/results/experiment_run_gpt-4_1-mini.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\proyectos\emf-kaizen-experiments\2026-ECMFA\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\proyectos\emf-kaizen-experiments\2026-ECMFA\RQ1\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8868B6-4771-4145-B9D8-CD30E597B17E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0B4BF95-A55B-4ED1-857B-C893FB9C270E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="783" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="eval run syntax" sheetId="3" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="76">
   <si>
     <t>Meta-models</t>
   </si>
@@ -173,15 +173,6 @@
     <t>Missing reference</t>
   </si>
   <si>
-    <t>No response</t>
-  </si>
-  <si>
-    <t>Response shown as text in chat</t>
-  </si>
-  <si>
-    <t>Other errors</t>
-  </si>
-  <si>
     <t>Has some elements repeated from the current model, unnecesarily</t>
   </si>
   <si>
@@ -276,6 +267,9 @@
   </si>
   <si>
     <t>domain</t>
+  </si>
+  <si>
+    <t>Incorrect intent</t>
   </si>
 </sst>
 </file>
@@ -679,7 +673,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -694,10 +688,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -709,13 +706,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1052,7 +1046,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S27"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.36328125" customWidth="1"/>
@@ -1061,20 +1055,20 @@
     <col min="4" max="11" width="11.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D3" s="34" t="s">
         <v>8</v>
       </c>
@@ -1083,16 +1077,16 @@
         <v>9</v>
       </c>
       <c r="G3" s="35"/>
-      <c r="H3" s="36" t="s">
+      <c r="H3" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="37"/>
-      <c r="J3" s="36" t="s">
+      <c r="I3" s="43"/>
+      <c r="J3" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="37"/>
-    </row>
-    <row r="4" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K3" s="43"/>
+    </row>
+    <row r="4" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -1138,18 +1132,12 @@
       <c r="P4">
         <v>4</v>
       </c>
-      <c r="Q4">
-        <v>5</v>
-      </c>
-      <c r="R4">
-        <v>6</v>
-      </c>
-      <c r="S4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="31" t="s">
+      <c r="Q4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="38" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -1183,14 +1171,14 @@
         <v>1</v>
       </c>
       <c r="L5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="M5">
         <f>COUNTIF($D5:$K7,M4)</f>
         <v>23</v>
       </c>
       <c r="N5">
-        <f t="shared" ref="N5:R5" si="0">COUNTIF($D5:$K7,N4)</f>
+        <f t="shared" ref="N5:P5" si="0">COUNTIF($D5:$K7,N4)</f>
         <v>0</v>
       </c>
       <c r="O5">
@@ -1202,19 +1190,11 @@
         <v>0</v>
       </c>
       <c r="Q5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <f>SUM(M5:R5)</f>
+        <f>SUM(M5:P5)</f>
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="32"/>
       <c r="B6" s="5" t="s">
         <v>3</v>
@@ -1247,14 +1227,14 @@
         <v>3</v>
       </c>
       <c r="L6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M6">
         <f>100*M5/24</f>
         <v>95.833333333333329</v>
       </c>
       <c r="N6">
-        <f t="shared" ref="N6:R6" si="1">100*N5/24</f>
+        <f t="shared" ref="N6:P6" si="1">100*N5/24</f>
         <v>0</v>
       </c>
       <c r="O6">
@@ -1265,16 +1245,8 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Q6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="7" spans="1:17" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="33"/>
       <c r="B7" s="6" t="s">
         <v>4</v>
@@ -1307,8 +1279,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="38" t="s">
+    <row r="8" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="39" t="s">
         <v>20</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -1342,14 +1314,14 @@
         <v>1</v>
       </c>
       <c r="L8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="M8">
         <f>COUNTIF($D8:$K10,M4)</f>
         <v>20</v>
       </c>
       <c r="N8">
-        <f t="shared" ref="N8:R8" si="2">COUNTIF($D8:$K10,N4)</f>
+        <f t="shared" ref="N8:P8" si="2">COUNTIF($D8:$K10,N4)</f>
         <v>0</v>
       </c>
       <c r="O8">
@@ -1361,20 +1333,12 @@
         <v>0</v>
       </c>
       <c r="Q8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <f>SUM(M8:R8)</f>
+        <f>SUM(M8:P8)</f>
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="39"/>
+    <row r="9" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="40"/>
       <c r="B9" s="5" t="s">
         <v>3</v>
       </c>
@@ -1406,14 +1370,14 @@
         <v>1</v>
       </c>
       <c r="L9" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M9">
         <f>100*M8/24</f>
         <v>83.333333333333329</v>
       </c>
       <c r="N9">
-        <f t="shared" ref="N9:R9" si="3">100*N8/24</f>
+        <f t="shared" ref="N9:P9" si="3">100*N8/24</f>
         <v>0</v>
       </c>
       <c r="O9">
@@ -1424,17 +1388,9 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q9">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="40"/>
+    </row>
+    <row r="10" spans="1:17" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="41"/>
       <c r="B10" s="6" t="s">
         <v>4</v>
       </c>
@@ -1466,8 +1422,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="31" t="s">
+    <row r="11" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="38" t="s">
         <v>2</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -1501,14 +1457,14 @@
         <v>1</v>
       </c>
       <c r="L11" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="M11">
         <f>COUNTIF($D11:$K13,M4)</f>
         <v>19</v>
       </c>
       <c r="N11">
-        <f t="shared" ref="N11:R11" si="4">COUNTIF($D11:$K13,N4)</f>
+        <f t="shared" ref="N11:P11" si="4">COUNTIF($D11:$K13,N4)</f>
         <v>0</v>
       </c>
       <c r="O11">
@@ -1520,19 +1476,11 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="R11">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <f>SUM(M11:R11)</f>
+        <f>SUM(M11:P11)</f>
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="32"/>
       <c r="B12" s="5" t="s">
         <v>3</v>
@@ -1565,14 +1513,14 @@
         <v>3</v>
       </c>
       <c r="L12" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M12">
         <f>100*M11/24</f>
         <v>79.166666666666671</v>
       </c>
       <c r="N12">
-        <f t="shared" ref="N12:R12" si="5">100*N11/24</f>
+        <f t="shared" ref="N12:P12" si="5">100*N11/24</f>
         <v>0</v>
       </c>
       <c r="O12">
@@ -1583,16 +1531,8 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q12">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="13" spans="1:17" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="33"/>
       <c r="B13" s="6" t="s">
         <v>4</v>
@@ -1625,8 +1565,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="31" t="s">
+    <row r="14" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="38" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -1660,14 +1600,14 @@
         <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="M14">
         <f>COUNTIF($D14:$K16,M4)</f>
         <v>24</v>
       </c>
       <c r="N14">
-        <f t="shared" ref="N14:R14" si="6">COUNTIF($D14:$K16,N4)</f>
+        <f t="shared" ref="N14:P14" si="6">COUNTIF($D14:$K16,N4)</f>
         <v>0</v>
       </c>
       <c r="O14">
@@ -1679,19 +1619,11 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R14">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <f>SUM(M14:R14)</f>
+        <f>SUM(M14:P14)</f>
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="32"/>
       <c r="B15" s="5" t="s">
         <v>3</v>
@@ -1724,14 +1656,14 @@
         <v>1</v>
       </c>
       <c r="L15" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M15">
         <f>100*M14/24</f>
         <v>100</v>
       </c>
       <c r="N15">
-        <f t="shared" ref="N15:R15" si="7">100*N14/24</f>
+        <f t="shared" ref="N15:P15" si="7">100*N14/24</f>
         <v>0</v>
       </c>
       <c r="O15">
@@ -1742,16 +1674,8 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="Q15">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R15">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="16" spans="1:17" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="33"/>
       <c r="B16" s="6" t="s">
         <v>4</v>
@@ -1784,8 +1708,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="31" t="s">
+    <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="38" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="11" t="s">
@@ -1819,14 +1743,14 @@
         <v>2</v>
       </c>
       <c r="L17" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="M17">
         <f>COUNTIF($D17:$K19,M4)</f>
         <v>22</v>
       </c>
       <c r="N17">
-        <f t="shared" ref="N17:R17" si="8">COUNTIF($D17:$K19,N4)</f>
+        <f t="shared" ref="N17:P17" si="8">COUNTIF($D17:$K19,N4)</f>
         <v>1</v>
       </c>
       <c r="O17">
@@ -1838,19 +1762,11 @@
         <v>0</v>
       </c>
       <c r="Q17">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="R17">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <f>SUM(M17:R17)</f>
+        <f>SUM(M17:P17)</f>
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="32"/>
       <c r="B18" s="5" t="s">
         <v>3</v>
@@ -1883,14 +1799,14 @@
         <v>3</v>
       </c>
       <c r="L18" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M18">
         <f>100*M17/24</f>
         <v>91.666666666666671</v>
       </c>
       <c r="N18">
-        <f t="shared" ref="N18:R18" si="9">100*N17/24</f>
+        <f t="shared" ref="N18:P18" si="9">100*N17/24</f>
         <v>4.166666666666667</v>
       </c>
       <c r="O18">
@@ -1901,16 +1817,8 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Q18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="R18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="33"/>
       <c r="B19" s="6" t="s">
         <v>4</v>
@@ -1943,15 +1851,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="E21" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>39</v>
       </c>
@@ -1970,7 +1878,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B23">
         <v>2</v>
       </c>
@@ -1978,15 +1886,15 @@
         <v>41</v>
       </c>
       <c r="E23">
-        <f t="shared" ref="E23:E27" si="10">COUNTIF(D$5:K$19,B23)</f>
+        <f t="shared" ref="E23:E25" si="10">COUNTIF(D$5:K$19,B23)</f>
         <v>1</v>
       </c>
       <c r="F23">
-        <f t="shared" ref="F23:F27" si="11">100*E23/(15*8)</f>
+        <f t="shared" ref="F23:F25" si="11">100*E23/(15*8)</f>
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B24">
         <v>3</v>
       </c>
@@ -2002,50 +1910,18 @@
         <v>9.1666666666666661</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B25">
         <v>4</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="E25">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F25">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="B26">
-        <v>5</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E26">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="B27">
-        <v>6</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E27">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="F27">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
@@ -2082,7 +1958,7 @@
         <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -2095,14 +1971,14 @@
         <v>9</v>
       </c>
       <c r="G3" s="35"/>
-      <c r="H3" s="42" t="s">
+      <c r="H3" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43" t="s">
+      <c r="I3" s="37"/>
+      <c r="J3" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="43"/>
+      <c r="K3" s="37"/>
     </row>
     <row r="4" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
@@ -2139,14 +2015,14 @@
         <v>16</v>
       </c>
       <c r="N4" s="27" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="O4" s="27" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="38" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -2230,7 +2106,7 @@
         <v>2</v>
       </c>
       <c r="M6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="N6">
         <f t="shared" ref="N6:N7" si="0">COUNTIF(D$5:K$7,L6)</f>
@@ -2277,7 +2153,7 @@
         <v>3</v>
       </c>
       <c r="M7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="N7">
         <f t="shared" si="0"/>
@@ -2289,7 +2165,7 @@
       </c>
     </row>
     <row r="8" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="39" t="s">
         <v>20</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -2338,7 +2214,7 @@
       </c>
     </row>
     <row r="9" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="39"/>
+      <c r="A9" s="40"/>
       <c r="B9" s="5" t="s">
         <v>3</v>
       </c>
@@ -2373,7 +2249,7 @@
         <v>2</v>
       </c>
       <c r="M9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="N9">
         <f t="shared" ref="N9:N10" si="2">COUNTIF(D$8:K$10,L9)</f>
@@ -2385,7 +2261,7 @@
       </c>
     </row>
     <row r="10" spans="1:15" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="40"/>
+      <c r="A10" s="41"/>
       <c r="B10" s="6" t="s">
         <v>4</v>
       </c>
@@ -2420,7 +2296,7 @@
         <v>3</v>
       </c>
       <c r="M10" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="N10">
         <f t="shared" si="2"/>
@@ -2432,7 +2308,7 @@
       </c>
     </row>
     <row r="11" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="31" t="s">
+      <c r="A11" s="38" t="s">
         <v>2</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -2516,7 +2392,7 @@
         <v>2</v>
       </c>
       <c r="M12" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="N12">
         <f t="shared" ref="N12:N13" si="3">COUNTIF(D$11:K$13,L12)</f>
@@ -2563,7 +2439,7 @@
         <v>3</v>
       </c>
       <c r="M13" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="N13">
         <f t="shared" si="3"/>
@@ -2575,7 +2451,7 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="38" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -2659,7 +2535,7 @@
         <v>2</v>
       </c>
       <c r="M15" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="N15">
         <f t="shared" ref="N15:N16" si="4">COUNTIF(D$14:K$16,L15)</f>
@@ -2706,7 +2582,7 @@
         <v>3</v>
       </c>
       <c r="M16" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="N16">
         <f t="shared" si="4"/>
@@ -2718,7 +2594,7 @@
       </c>
     </row>
     <row r="17" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="41" t="s">
+      <c r="A17" s="31" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="11" t="s">
@@ -2802,7 +2678,7 @@
         <v>2</v>
       </c>
       <c r="M18" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="N18">
         <f t="shared" ref="N18:N19" si="5">COUNTIF(D$17:K$19,L18)</f>
@@ -2849,7 +2725,7 @@
         <v>3</v>
       </c>
       <c r="M19" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="N19">
         <f t="shared" si="5"/>
@@ -2862,10 +2738,10 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="F21" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G21" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
@@ -2892,7 +2768,7 @@
         <v>2</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F23">
         <f>COUNTIF(D$5:K$19,B23)</f>
@@ -2908,7 +2784,7 @@
         <v>3</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F24">
         <f>COUNTIF(D$5:K$19,B24)</f>
@@ -2951,7 +2827,7 @@
         <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -2964,14 +2840,14 @@
         <v>9</v>
       </c>
       <c r="G3" s="35"/>
-      <c r="H3" s="36" t="s">
+      <c r="H3" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="37"/>
-      <c r="J3" s="36" t="s">
+      <c r="I3" s="43"/>
+      <c r="J3" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="37"/>
+      <c r="K3" s="43"/>
     </row>
     <row r="4" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
@@ -3008,14 +2884,14 @@
         <v>16</v>
       </c>
       <c r="N4" s="27" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="O4" s="27" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="38" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -3052,7 +2928,7 @@
         <v>1</v>
       </c>
       <c r="M5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="N5">
         <f>COUNTIF(D$5:K$7,L5)</f>
@@ -3099,7 +2975,7 @@
         <v>2</v>
       </c>
       <c r="M6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="N6">
         <f t="shared" ref="N6:N7" si="0">COUNTIF(D$5:K$7,L6)</f>
@@ -3146,7 +3022,7 @@
         <v>3</v>
       </c>
       <c r="M7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="N7">
         <f t="shared" si="0"/>
@@ -3158,7 +3034,7 @@
       </c>
     </row>
     <row r="8" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="39" t="s">
         <v>20</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -3195,7 +3071,7 @@
         <v>1</v>
       </c>
       <c r="M8" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="N8">
         <f>COUNTIF(D$8:K$10,L8)</f>
@@ -3207,7 +3083,7 @@
       </c>
     </row>
     <row r="9" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="39"/>
+      <c r="A9" s="40"/>
       <c r="B9" s="5" t="s">
         <v>3</v>
       </c>
@@ -3242,7 +3118,7 @@
         <v>2</v>
       </c>
       <c r="M9" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="N9">
         <f t="shared" ref="N9:N10" si="2">COUNTIF(D$8:K$10,L9)</f>
@@ -3254,7 +3130,7 @@
       </c>
     </row>
     <row r="10" spans="1:15" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="40"/>
+      <c r="A10" s="41"/>
       <c r="B10" s="6" t="s">
         <v>4</v>
       </c>
@@ -3289,7 +3165,7 @@
         <v>3</v>
       </c>
       <c r="M10" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="N10">
         <f t="shared" si="2"/>
@@ -3301,7 +3177,7 @@
       </c>
     </row>
     <row r="11" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="31" t="s">
+      <c r="A11" s="38" t="s">
         <v>2</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -3338,7 +3214,7 @@
         <v>1</v>
       </c>
       <c r="M11" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="N11">
         <f>COUNTIF(D$11:K$13,L11)</f>
@@ -3385,7 +3261,7 @@
         <v>2</v>
       </c>
       <c r="M12" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="N12">
         <f t="shared" ref="N12:N13" si="3">COUNTIF(D$11:K$13,L12)</f>
@@ -3432,7 +3308,7 @@
         <v>3</v>
       </c>
       <c r="M13" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="N13">
         <f t="shared" si="3"/>
@@ -3444,7 +3320,7 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="38" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -3481,7 +3357,7 @@
         <v>1</v>
       </c>
       <c r="M14" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="N14">
         <f>COUNTIF(D$14:K$16,L14)</f>
@@ -3528,7 +3404,7 @@
         <v>2</v>
       </c>
       <c r="M15" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="N15">
         <f t="shared" ref="N15:N16" si="4">COUNTIF(D$14:K$16,L15)</f>
@@ -3575,7 +3451,7 @@
         <v>3</v>
       </c>
       <c r="M16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="N16">
         <f t="shared" si="4"/>
@@ -3587,7 +3463,7 @@
       </c>
     </row>
     <row r="17" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="31" t="s">
+      <c r="A17" s="38" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="11" t="s">
@@ -3624,7 +3500,7 @@
         <v>1</v>
       </c>
       <c r="M17" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="N17">
         <f>COUNTIF(D$17:K$19,L17)</f>
@@ -3671,7 +3547,7 @@
         <v>2</v>
       </c>
       <c r="M18" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="N18">
         <f t="shared" ref="N18:N19" si="5">COUNTIF(D$17:K$19,L18)</f>
@@ -3718,7 +3594,7 @@
         <v>3</v>
       </c>
       <c r="M19" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="N19">
         <f t="shared" si="5"/>
@@ -3731,10 +3607,10 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="D21" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E21" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
@@ -3745,7 +3621,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D22">
         <f>COUNTIF(D$5:K$19,B22)</f>
@@ -3761,7 +3637,7 @@
         <v>2</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D23">
         <f t="shared" ref="D23:D24" si="6">COUNTIF(D$5:K$19,B23)</f>
@@ -3777,7 +3653,7 @@
         <v>3</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D24">
         <f t="shared" si="6"/>
@@ -3820,7 +3696,7 @@
         <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -3833,16 +3709,16 @@
         <v>9</v>
       </c>
       <c r="G3" s="35"/>
-      <c r="H3" s="36" t="s">
+      <c r="H3" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="37"/>
-      <c r="J3" s="36" t="s">
+      <c r="I3" s="43"/>
+      <c r="J3" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="37"/>
+      <c r="K3" s="43"/>
       <c r="M3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3883,17 +3759,17 @@
         <v>8</v>
       </c>
       <c r="N4" s="28" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="O4" s="28" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="P4" s="28" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="38" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -4051,7 +3927,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="39" t="s">
         <v>20</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -4085,7 +3961,7 @@
         <v>3</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="M8">
         <f>SUM(M5:M7)</f>
@@ -4105,7 +3981,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="39"/>
+      <c r="A9" s="40"/>
       <c r="B9" s="5" t="s">
         <v>3</v>
       </c>
@@ -4139,7 +4015,7 @@
       <c r="L9" s="1"/>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="40"/>
+      <c r="A10" s="41"/>
       <c r="B10" s="6" t="s">
         <v>4</v>
       </c>
@@ -4173,7 +4049,7 @@
       <c r="L10" s="1"/>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="31" t="s">
+      <c r="A11" s="38" t="s">
         <v>2</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -4277,7 +4153,7 @@
       <c r="L13" s="1"/>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="38" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -4381,7 +4257,7 @@
       <c r="L16" s="1"/>
     </row>
     <row r="17" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="31" t="s">
+      <c r="A17" s="38" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="11" t="s">
@@ -4486,10 +4362,10 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="D21" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E21" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.35">
@@ -4500,7 +4376,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D22">
         <f>COUNTIF(D$5:K$19,B22)</f>
@@ -4516,7 +4392,7 @@
         <v>2</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D23">
         <f t="shared" ref="D23:D24" si="4">COUNTIF(D$5:K$19,B23)</f>
@@ -4532,7 +4408,7 @@
         <v>3</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D24">
         <f t="shared" si="4"/>
@@ -4575,7 +4451,7 @@
         <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -4588,16 +4464,16 @@
         <v>9</v>
       </c>
       <c r="G3" s="35"/>
-      <c r="H3" s="36" t="s">
+      <c r="H3" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="37"/>
-      <c r="J3" s="36" t="s">
+      <c r="I3" s="43"/>
+      <c r="J3" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="37"/>
+      <c r="K3" s="43"/>
       <c r="M3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4635,20 +4511,20 @@
         <v>16</v>
       </c>
       <c r="M4" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="N4" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="O4" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="P4" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="N4" s="29" t="s">
-        <v>75</v>
-      </c>
-      <c r="O4" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="P4" s="29" t="s">
-        <v>77</v>
-      </c>
     </row>
     <row r="5" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="38" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -4765,7 +4641,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="39" t="s">
         <v>20</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -4816,7 +4692,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="39"/>
+      <c r="A9" s="40"/>
       <c r="B9" s="5" t="s">
         <v>3</v>
       </c>
@@ -4849,7 +4725,7 @@
       </c>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="40"/>
+      <c r="A10" s="41"/>
       <c r="B10" s="6" t="s">
         <v>4</v>
       </c>
@@ -4882,7 +4758,7 @@
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="31" t="s">
+      <c r="A11" s="38" t="s">
         <v>2</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -4999,7 +4875,7 @@
       </c>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="38" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -5116,7 +4992,7 @@
       </c>
     </row>
     <row r="17" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="31" t="s">
+      <c r="A17" s="38" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="11" t="s">
@@ -5252,7 +5128,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B21">
         <f>SUM(D5:K19)/120</f>
@@ -5261,7 +5137,7 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B22">
         <f>MIN(D5:K19)</f>
@@ -5270,7 +5146,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B23">
         <f>MAX(D5:K19)</f>
@@ -5279,7 +5155,6 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A14:A16"/>
     <mergeCell ref="A17:A19"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="F3:G3"/>
@@ -5288,6 +5163,7 @@
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A14:A16"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:K19">
     <cfRule type="colorScale" priority="1">
@@ -5321,7 +5197,7 @@
         <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -5334,16 +5210,16 @@
         <v>9</v>
       </c>
       <c r="G3" s="35"/>
-      <c r="H3" s="36" t="s">
+      <c r="H3" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="37"/>
-      <c r="J3" s="36" t="s">
+      <c r="I3" s="43"/>
+      <c r="J3" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="37"/>
+      <c r="K3" s="43"/>
       <c r="M3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -5381,20 +5257,20 @@
         <v>16</v>
       </c>
       <c r="M4" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="N4" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="O4" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="P4" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="N4" s="29" t="s">
-        <v>75</v>
-      </c>
-      <c r="O4" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="P4" s="29" t="s">
-        <v>77</v>
-      </c>
     </row>
     <row r="5" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="38" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -5511,7 +5387,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="39" t="s">
         <v>20</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -5562,7 +5438,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="39"/>
+      <c r="A9" s="40"/>
       <c r="B9" s="5" t="s">
         <v>3</v>
       </c>
@@ -5595,7 +5471,7 @@
       </c>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="40"/>
+      <c r="A10" s="41"/>
       <c r="B10" s="6" t="s">
         <v>4</v>
       </c>
@@ -5628,7 +5504,7 @@
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="31" t="s">
+      <c r="A11" s="38" t="s">
         <v>2</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -5745,7 +5621,7 @@
       </c>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="38" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -5862,7 +5738,7 @@
       </c>
     </row>
     <row r="17" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="31" t="s">
+      <c r="A17" s="38" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="11" t="s">
@@ -5998,7 +5874,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B21">
         <f>SUM(D5:K19)/120</f>
@@ -6007,7 +5883,7 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B22">
         <f>MIN(D5:K19)</f>
@@ -6016,7 +5892,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B23">
         <f>MAX(D5:K19)</f>
@@ -6068,7 +5944,7 @@
         <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -6081,16 +5957,16 @@
         <v>9</v>
       </c>
       <c r="G3" s="35"/>
-      <c r="H3" s="42" t="s">
+      <c r="H3" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43" t="s">
+      <c r="I3" s="37"/>
+      <c r="J3" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="43"/>
+      <c r="K3" s="37"/>
       <c r="M3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6128,20 +6004,20 @@
         <v>16</v>
       </c>
       <c r="M4" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="N4" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="O4" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="P4" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="N4" s="29" t="s">
-        <v>75</v>
-      </c>
-      <c r="O4" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="P4" s="29" t="s">
-        <v>77</v>
-      </c>
     </row>
     <row r="5" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="38" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -6258,7 +6134,7 @@
       </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="39" t="s">
         <v>20</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -6309,7 +6185,7 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="39"/>
+      <c r="A9" s="40"/>
       <c r="B9" s="5" t="s">
         <v>3</v>
       </c>
@@ -6342,7 +6218,7 @@
       </c>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="40"/>
+      <c r="A10" s="41"/>
       <c r="B10" s="6" t="s">
         <v>4</v>
       </c>
@@ -6375,7 +6251,7 @@
       </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="31" t="s">
+      <c r="A11" s="38" t="s">
         <v>2</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -6492,7 +6368,7 @@
       </c>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="38" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -6609,7 +6485,7 @@
       </c>
     </row>
     <row r="17" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="41" t="s">
+      <c r="A17" s="31" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="11" t="s">
@@ -6745,7 +6621,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="L21" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="M21">
         <f>MEDIAN(D5:E19)</f>
@@ -6769,13 +6645,13 @@
         <v>39</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22" t="s">
         <v>50</v>
       </c>
-      <c r="D22" t="s">
-        <v>53</v>
-      </c>
       <c r="E22" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F22">
         <f>MEDIAN(D5:K19)</f>
@@ -6784,7 +6660,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="E23" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F23">
         <f>MIN(D5:K19)</f>
@@ -6793,7 +6669,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="E24" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F24">
         <f>MAX(D5:K19)</f>
